--- a/script/templates/IndicatoriCatalogo_BS.xlsx
+++ b/script/templates/IndicatoriCatalogo_BS.xlsx
@@ -2,23 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Catalogo Indicatori BS" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catalogo Indicatori BS'!$E$1:$E$236</definedName>
-  </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,24 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E79"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,14 +46,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -428,43 +413,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G236"/>
+  <dimension ref="A1:G418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Codice Indicatore</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Indicatore</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Descrizione sintetica</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Tipologia</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Codice UOC Referente</t>
         </is>
@@ -8176,7 +8154,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Proporzione di pazienti talassemici trasfusione dipendenti con ferritina ≤ 1500 ng/ml</t>
+          <t>Proporzione di pazienti talassemici trasfusione dipendenti con ferritina &lt;= 1500 ng/ml</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8545,8 +8523,6254 @@
         </is>
       </c>
     </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>A03</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Indicatore H04Z - Rapporto tra i ricoveri attribuiti a  DRG ad alto rischio di inappropriatezza e ricoveri attribuiti a DRG non a rischio di inappropriatezza in regime ordinario.</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Ob. CORE NSG - Dimissioni con DRG "inappropriato" da strutture pubbliche e private accreditate per residenti e non residenti in modalità ordinaria per acuti.</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>BSU7200</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Flusso SDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>A03B</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Indicatore H04Z - Rapporto tra i ricoveri attribuiti a  DRG ad alto rischio di inappropriatezza e ricoveri attribuiti a DRG non a rischio di inappropriatezza in regime ordinario.</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Ob. CORE NSG - Dimissioni con DRG "inappropriato" da strutture pubbliche e private accreditate per residenti e non residenti in modalità ordinaria per acuti.</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>BSU7200</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Flusso SDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>A03C</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Indicatore H04Z - Rapporto tra i ricoveri attribuiti a  DRG ad alto rischio di inappropriatezza e ricoveri attribuiti a DRG non a rischio di inappropriatezza in regime ordinario.</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Ob. CORE NSG - Dimissioni con DRG "inappropriato" da strutture pubbliche e private accreditate per residenti e non residenti in modalità ordinaria per acuti.</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>BSU7200</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Flusso SDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>A101</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Volumi di interventi chirurgici per procedure testa-collo anno 2026.</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Consolidamento interventi chirurgici otorinolaringoiatria testa-collo.</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>BSU7200</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Flussi aziendali</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>A13</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Percentuale di verbali redatti dopo l'intervento chirurgico.</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Decisione collegiale multisciplinare sul programma terapeutico per pazienti oncologici.</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>BSOP3310</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Piattaforma ROC</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>A17</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Avvenuta attivazione percorso per metodiche alternative della chirurgia della tiroide e paratiroide.</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Attivazione di percorso per metodiche alternative della chirurgia della tiroide e paratiroide.</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>BSCS1405</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Relazione capo dipartimento</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>A21</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Attivazione percorso diagnostico e terapeutico aziendale per MIASTENIA GRAVIS.</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Percorso diagnostico e terapeutico aziendale per MIASTENIA GRAVIS.</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Relazione capo dipartimento</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>A27</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>tumore maligno della mammella.</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Percorsi diagnostici combinati con ENG-EMG ed ecografia nelle lesioni traumatiche e compressive del sistema nervoso periferico.</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>A28</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Percentuali di dimissioni effettuate nel 36 ore.</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Dimissioni entro 36 ore.</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>BSU7200</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Flussi aziendali</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>A31</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Attivazione della classificazione prestazioni interne in classi di complessità in relazione alla sede di esecuzione.</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Classificazione prestazioni interne in classi di complessità in relazione alla sede di esecuzione.</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Relazione capo dipartimento</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>A33</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Attivazione percorsi ambulatoriali complessi e coordinati (PACC).</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Percorsi ambulatoriali complessi e coordinati (PACC).</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>A36</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Percentuale di incremento Televisita per pazienti eleggibili affetti da fibrosi polmonare ed asma grave in trattamento cronico verso anno 2025.</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Potenziamento sanità digitale: percorsi di telemedicina. Televisita per pazienti eleggibili affetti da fibrosi polmonare ed asma grave in trattamento cronico.</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>BAA9909</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Software fornitore Gesan</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>A37B</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Percentuale di consulenze in Day Hospital evase entro le 48h.</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Rispetto tempi di attesa consulenza per pazienti diabetici.</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>BAA9909</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Software Wirgilio</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>A40</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Percentuale di riduzione dei DH vs. 2024.</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Conversione dei Day Hospital in PACC e/o prestazioni ambulatoriali.</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>BSU7200</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Flussi aziendali</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>A45</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Percentuale di pazienti con attesa inferiore ai tre giorni.</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Riduzione tempi di attesa del paziente onco-ematologico</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>BSA9090</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>CUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>A46</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Percentuale di pazienti dei DH converiti in PACC.</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Conversione dei Day Hospital in PACC relativi ai follow-up dopo un anno dei pazienti trapiantati di fegato.</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>BSU7200</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Flussi aziendali</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>A47</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Percentuale di incremento annuale.</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Incentivazione attività di DH per i pazienti provenienti dal P.S. per trattamento con Ferrinject.</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>BSMP1300</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Flussi aziendali</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>A47C</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Percentuale di pazienti trattati infusi con trattamento Ferrinject.</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Consolidamento attività di DH per i pazienti provenienti dal P.S. per trattamento con Ferrinject.</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Flussi aziendali</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>A48</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Attivazione dei DH terapeutici.</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Trasferimento di pazienti in degenza ordinaria verso l'attività di DH terapeutici.</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>BSA9090</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>CUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>A49</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Percentuale di pazienti dei DH converiti in PACC.</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Conversione dei Day Hospital in PACC per i pazienti talassemici.</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>BSU7200</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Flussi aziendali</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>A50</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Percentuale di incremento semestre 2/2025 verso semestre 1/2025.</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Potenziamento dell'attrattività extra-regione.</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>BSU7200</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Flusso SDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>A57</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Percentuale di viraggio ai PACC dei DH diagnostici/chemioterapici.</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Implementazione percorsi ambulatoriali complessi e coordinati.</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>BSA9090</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>CUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>A57B</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Percentuale di viraggio ai PACC dei DH diagnostici/chemioterapici.</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Implementazione percorsi ambulatoriali complessi e coordinati.</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>BSA9090</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>CUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>A58</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Percentuale pazienti oncologici deospedalizzati da PS/OBI dopo consulenza specialistica.</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Pazienti deospedalizzati da PS/OBI dopo consulenza specialistica.</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>BAA9909</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Software Wirgilio</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>A65</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Partecipazione, e completamento, di 3 moduli da parte del 50% del personale al corso PNRR sulle infezioni correlate all'assistenza entro il 30/06/2025.</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Frequenza al corso PNRR sulle infezioni correlate all'assistenza.</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>BSU4700</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Flussi aziendali</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>A67</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Attivazione percorso ultrafiltrazione pazienti epatopatici.</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Percorso ultrafiltrazione pazienti epatopatici.</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>A68</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Attivazione percorso endoscopie in sedazione.</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Percorso endoscopie in sedazione.</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>A72</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Attivazione percorso tracciabilità informatica delle trasfusioni per l'azienda.</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Percorso tracciabilità informatica delle trasfusioni per l'azienda.</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>A73</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Tempi di validazione delle unità di sangue dalla donazione alla pronta disponibilità max 48 ore.</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Disponbilità delle unità di sangue dalle donazioni.</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>BSTA4010</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Flussi aziendali</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>A76</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Percentuale di incremento dell'attività di diagnostica per i pazienti interni.</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Incentivazione dell'attività di diagnostica strumentale: ecocardiografia, doppler, doppler vascolare, holter ECG, holter pressione arteriosa ed ecoaddome per i pazienti interni.</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>BSU7200</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Flusso SDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>A77</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Percentuale di incremento dell'attività di diagnostica per i pazienti interni.</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Incentivazione dell'attività di diagnostica strumentale: ecocardiografia, holter pressorio eco-doppler artero-venoso degli arti inferiori per i pazienti interni.</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>BSU7200</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Flusso SDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>A78</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Percentuale di incremento dell'attività di diagnostica per i pazienti esterni.</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Incentivazione dell'attività di diagnostica strumentale: ecocardiografia, holter pressorio eco-doppler artero-venoso degli arti ineferiori per i pazienti esterni.</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>BSA9090</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>CUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>A81</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Attivazione ambulatorio malattie rare endocrine in collaborazione con altre UOC e istituti di ricerca.</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Ambulatorio malattie rare endocrine.</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>A82D</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Percentuale di SDO chiuse in 30 giorni dalla data di dimissione del paziente dal DH.</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Adeguatezza nella compilazione della Scheda di Dimissione Ospedaliera (SDO) dei Day Hospital.</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>BSU7200</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Flusso SDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>A93</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Percentuale di incremento nutrizione enterale verso anno 2025.</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Appropriatezza nell'utilizzo della nutrizione enterale.</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>BSTA4800-1</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Flussi aziendali</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Utilizzo della sola cartella clinica ambulatoriale e della cartella clinica PACC  informatizzate.</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Utilizzo della cartella clinica ambulatoriale e della cartella clinica PACC informatizzate.</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>AREA_ESITI</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Software Wirgilio/CUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>E14</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Residuo liste di attesa chirurgiche al 2023.</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Monitoraggio gestione pazienti in lista di attesa chirurgica, codici di priorità C e D.</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>AREA_ESITI</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>BSA9090</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>CUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>E19</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Pubblicazione di articoli scientifici su riviste indicizzate.</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Incrementare partecipazione a studi multicentrici e trial clinici.</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>AREA_ESITI</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Percentuale di analisi di campioni citologici effettuati</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Valutazione di adeguatezza al microscopico dei prelievi effettuati in pneumologia interventistica (solo su richiesta).</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>AREA_SERV_SAN</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>BSTA4600</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Software UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>S17</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Avvenuta realizzazione di procedura.</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Definizione di una procedura aziendale per l'erogazione di prestazioni in service verso altre strutture sanitarie.</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>AREA_SERV_SAN</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>BSA9090</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Rilascio procedura</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>S18</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Report trimestrale.</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Implementazione attività di sorveglianza ESBL ( beta- lattamasi a spettro esteso) nelle Enterobacteriaceae.</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>AREA_SERV_SAN</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>BSTA5000</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>S19</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Percentuale di campioni refertati con riduzione tempo medio vs anno precedente &gt;= 4 giorni.</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Riduzione media di 4 giorni lavorativi per una percentuale dei campioni effettuati dei tempi di attesa referti test anticorpi anti-Recettore dell'acetilcolina (AChR-Ab).</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>AREA_SERV_SAN</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>BSTA5000</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Software Open-Lis</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Percentuale di campioni refertati con riduzione tempo medio vs anno precedente &gt;= 4 giorni.</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Riduzione media di 4 giorni lavorativi per una percentuale dei campioni effettuati dei tempi di attesa referti test anticorpi anti-muscolo specifico recettore tirosin kinasi( MuSK-Ab).</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>AREA_SERV_SAN</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>BSTA5000</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Software UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>S28</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Redazione procedura per l'attivazione di un Centro di ascolto (dirigenti psicologi) rivolto ai dipendenti a rischio stress-correlato.</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Procedura per l'attivazione di un Centro di ascolto rivolto ai dipendenti a rischio stress-correlato.</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>AREA_SERV_SAN</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>BSU1409</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>S30</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Adeguamento e monitoraggio Posti Letto su piattaforma informatica Wirgilio-CPI a seguito delle diverse esigenze aziendali</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Attività di monitoraggio finalizzata alla riorganizzazione dei posti letto su piattaforma informatica Wirgilio-CPI.</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>AREA_SERV_SAN</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>BSU1409</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>S31</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Attivazione del "Percorso Donna" dedicato alla diagnosi e del trattamento della “sindrome da congestione pelvica” (SCP).</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>“Percorso Donna” dedicato alla diagnosi e del trattamento della “sindrome da congestione pelvica” (SCP), patologia caratterizzata da un ristagno di sangue nelle vene pelviche, e che è causa di dolore pelvico cronico, spesso confuso con “ lombalgia” dismenorrea, dispareunia e sintomi correlati.</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>AREA_SERV_SAN</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>S32</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Attivazione percorso interno per pazienti provenienti dal G.O.M. differenziato dal follow-up</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Percorso interno per pazienti provenienti dal G.O.M. differenziato dal follow-up.</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>AREA_SERV_SAN</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>S34</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Mantenimento del numero di osservazioni per morte encefalica rispetto alla media ponderata degli ultimi 5 anni.</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Media osservazioni per morte encefalica annue.</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>AREA_SERV_SAN</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>BSU4500</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Flussi aziendali</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>S36</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Completamento iter medico-legale nulla osta alla cremazione.</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Autorizzazione alla cremazione di cadavere (D.P.R. n° 285 del 10.09.1990, legge 30 marzo 2001 n. 130).</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>AREA_SERV_SAN</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>BSU4500</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>S37</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Attivazione percorso erogazione primo ciclo di cura dei pazienti dimessi.</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Erogazione del primo ciclo terapeutico dei pazienti dimessi.</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>AREA_SERV_SAN</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>BSTA4800-1</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>S43</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Livello di qualità percepita dagli utenti relativamente ai servizi assistenziali.</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Somministrazione di questionari per la rilevazione della qualità dell'assistenza percepità dell'attività intramuraria in reparto.</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>BSU9208</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Microsoft Forms</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>S45</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Trasmissione flussi trimestrali pazienti ricoverati intramuraria.</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Trasmissione flussi pazienti ricoverati attività intramuraria.</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>AREA_SERV_SAN</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>BSU7200</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Flussi aziendali</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>S48</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Report trimestrale del coordinatore del complesso operatorio.</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Tracciabilità dei device in cartella clinica operatoria informatizzata.</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>AREA_SERV_SAN</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>BAA9909</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Software Wirgilio</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>S51</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Livello di qualità percepita dagli utenti relativamente ai servizi assistenziali.</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Somministrazione di questionari per la rilevazione della qualità dell'assistenza percepità dell'attività intramuraria in reparto.</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>AREA_SERV_SAN</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>BSU9208</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Microsoft Forms</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>S61</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Invio report trimestrale verifica giacenza fisica e contabile dei beni sanitari per i magazzini citati.</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Analisi giacenza fisica e contabile dei beni sanitari per i magazzini  BE7, BD6, BD7.</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>AREA_SERV_SAN</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Report coordinatore complesso operatorio</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>S61B</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Invio report trimestrale verifica giacenza fisica e contabile dei beni sanitari per i magazzini citati.</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Analisi giacenza fisica e contabile dei beni sanitari per il magazzino BC2.</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>AREA_SERV_SAN</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Report coordinatore complesso operatorio</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>S62</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Proporzione di slot saturati come da programmazione.</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Slot di sala operatoria saturati come da programmazione chirurgica settimanale.</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>AREA_SERV_SAN</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Report UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>ST01</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Alimentazione e tenuta del database sulle attività di tirocini curriculari in rete Intra e extra formativa.</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Attività di tirocini curriculari in rete Intra, extra formativa e frequenza volontaria.</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>BSU4700</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Report UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>ST02</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Mantenimento dei volumi di attività conto terzi in ambito di corsi di formazione frontali e pratici.</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Attività conto terzi in ambito di formazione frontale.</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>BSU4700</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Report UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>ST03</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Redazione di n. 2 relazioni semestrali sullo stato di avanzamento della Macroprogettazione del Piano Formativo Aziendale 2026</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Stato di avanzamento della Macroprogettazione relativa al Piano formativo Aziendale 2026</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>BSU4700</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Report UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>ST04</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Avvenuto accreditamento della struttura entro il 31/12/2026.</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Supporto all' Accreditamento per la Ricerca fase 1</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>BSU4700</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>ST05</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Percentuale di corsi attivati, comprese le riedizioni, in relazione alla Macroprogettazione per anno 2026</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Attuazione e completamento del piano formativo previsto per l'anno 2026.</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>BSU4700</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Report UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>ST06</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Riunioni quadrimestrali con i coordinatori /coordinatori dipartimentali per uniformare le attività di organizzazione e di coordinamento delle UU.OO.</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Appropriatezza dei processi organizzativi.</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>BSU9096</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>ST07</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Monitoraggio bimestrale di compilazione della documentazione infermieristica per ciascuna area dipartimentale.</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Monitoraggio compilazione della documentazione infermieristica integrata alla C.P.I. aziendale.</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>ST08</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Report mensile per il monitoraggio delle Lesioni da pressione nelle UU.OO.  di Medicina.</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Elaborazione di un report mensile per il monitoraggio delle Lesioni da pressione nelle UU.OO.  di Medicina (Med. 1 - Med. 2 - Med. 3 - Med. Ad ind. Ger.)</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>BSU9096</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>ST09</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Report mensile delle ore di lavoro in regime di straordinario dell'area comparto per U.O.</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Consuntivazione ore delle ore di lavoro in regime di straordinario dell'area comparto per U.O..</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>BSU9096</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>ST10</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Pianificazione formativa finalizzata all'omogeneità dell'agire professionale dei profili dell'area comparto.</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Uniformità ed omogeneità dell'agire professionale.</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>ST100</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Report quadrimestrale alle UU.OO aziendali con indicazione di azioni correttive</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Monitoraggio sistematico degli adempimenti amministrazione trasparente da parte delle UU.OO.</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Report UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>ST101</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Presentazione pratiche presso il competente comando dei VVFF.</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Redazione aggiornamenti esami progetto VVFF ex DM 19/03/2015.</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>ST102</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Avvenuta rendicontazione PNRR relativa alle attività svolte nel 2026, assicurando la verifica delle operazioni e la coerenza con i requisiti di monitoraggio e controllo.</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Completamento e rendicontazione dei progetti in essere finanziati da fondi dedicati, relativi ad interventi di manutenzione.</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>ST102B</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Avvenuta rendicontazione PNRR relativa alle attività svolte nel 2026, assicurando la verifica delle operazioni e la coerenza con i requisiti di monitoraggio e controllo.</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Completamento e rendicontazione dei progetti in essere a valere su fondi dedicati.</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>ST103</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Partecipazione al corso di formazione.</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Attività di formazione BIM -Manutenzione Edile ed Impiantistica.</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>BAA9907</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>ST104</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Completamento centrale alimentata a metano (per la produzione potenza termica 2700 KWh, potenza elettrica 1060 KWe)</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Completamento di una centrale di cogenerazione.</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>BAA9913</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>ST105</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Report quadrimestrale su output delle azioni di comunicazione traffico ed engagement sui social media (video,infografiche, grafiche)</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Campagne di comunicazione su temi specifici come la donazione sangue, l'accessibilità ai servizi ospedalieri, la donazione di organi e tessuti</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>BAA9912</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>ST106</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Percentuale di pagamenti pazienti stranieri acquisiti mediante polizza.</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Prestazioni fatturate a pazienti stranieri anno 2026. - Obiettivo condiviso UOC Gestione Economica e Finanziaria (GEF) e UOC Affari Generali -</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>BAA9905</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>ST107</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Avvenuta redazione del piano.</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Redazione del piano triennale degli investimenti</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>BAA9913</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>ST108</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Avvenuta redazione Regolamento per il rilascio copia conforme della documentazione sanitaria entro 31/07/2026</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Regolamento per il rilascio copia conforme della documentazione sanitaria.</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>BAA9912</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>ST11</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Job Description delle posizioni funzionali previste dal sistema degli incarichi.</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Incarichi, funzioni e posizioni funzionali.</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>ST12</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Pianificazione e relativa programmazione del fabbisogno per singola UOC di personale ruolo sanitario area comparto.</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Fabbisogno, per singola UOC, di personale ruolo sanitario area comparto.</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>ST13</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Fatture liquidate entro 30 gg., tempo medio di ritardo &lt;0.</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Rispetto dei tempi di pagamento.</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>Piattaforma Coopera
+Soresa</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>ST14</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Livelli di partecipazione dello staff.</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Supporto all'attività deliberativa.</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Relazione Direzione referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>ST15</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Totale ore annue di straordinario per dipendente come previsto da CCNL.</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Appropriatezza nel ricorso al lavoro straordinario.</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>BAA9903</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>Software G.O.P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>ST16</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Redazione report quadrimestrale e condivisione stati di avanzamento.</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Monitoring avanzamento formazione del personale da piattaforma "Syllabus".</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>Piattaforma Syllabus</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>ST17</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Attivazione corso di formazione.</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Formazione continua Privacy e Protezione dei Dati in Sanità: Tra tutela del paziente e obblighi amministrativi</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>BAA9912</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>ST17A</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Percentuale di personale afferente alla UOC che completa il percorso formativo, comprovato dai report di partecipazione.</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Formazione continua. Piattaforma Syllabus: "La strategia di prevenzione della corruzione e la trasparenza amministrativa."</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>Piattaforma Syllabus</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>ST17B</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Percentuale di personale afferente alla UOC che completa il percorso formativo, comprovato da report di partecipazione.</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Formazione continua. Piattaforma Syllabus: "Proteggere dati personali e la privacy."</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>BAA9908</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Piattaforma Syllabus</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>ST17C</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Percentuale di personale afferente alla UOC che completa il percorso formativo, comprovato da report di partecipazione.</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Formazione continua. Piattaforma Syllabus: "Proteggere dati personali e la privacy."</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>Piattaforma Syllabus</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>ST18</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Report quadrimestrale con evidenza delle anomalie rilevate da inviare alle UU.OO..</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Analisi della corretta imputazione delle voci nell'alimentazione dei Centri di Costo.</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>ST19</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Rendicontazione periodica sugli esiti dell'attività di internal audit svolte mediante l'utilizzo di check list.</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Internal audit, attività di controllo (di cui alla D.G.R.C. del 21/12/2024 n. 731).</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>BAA9912</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>Report UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>ST19B</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Monitoraggio e aggiornamento delle procedure amministrativo-contabili di cui al DCA 27/2019.</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Internal audit, attività di controllo (di cui alla D.G.R.C. del 21/12/2024 n. 731).</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>ST20</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Redazione capitolato tecnico di gara, entro il 30/04/2025.</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Procedura di gara ad evidenza pubblica fornitura in service di sistemi in automazione per indagini chimico-cliniche e immunochimiche ed ematologiche per il laboratorio dell’Azienda.</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>Pubblicazione delibera</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>ST20B</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Espletamento gara ad evidenza pubblica fornitura in service di sistemi in automazione per indagini chimico-cliniche e immunochimiche ed ematologiche per il laboratorio dell’Azienda.</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Procedura di gara ad evidenza pubblica fornitura in service di sistemi in automazione per indagini chimico-cliniche e immunochimiche ed ematologiche per il laboratorio dell’Azienda.</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>BAA9906</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>Pubblicazione delibera</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>ST21</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Aggiornamento delle procedure in essere in funzione della dinamicità dell’evoluzione delle strutture aziendali, nonché formazione degli addetti antincendio.</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Presa in carico referto POCT emogas da sanitario.</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>BAA9911</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>ST22</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Fabbisogno e verifica qualità dei D.P.I. approvvigionati e consegnati presso i magazzini aziendali. Valutazione preventiva delle richieste dei reparti.</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Fabbisogno e qualità dispositivi protezione individuale.</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>BAA9911</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>ST23</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Implementazione del Sistema di Gestione della Sicurezza sul Lavoro mediante: verifiche ispettive sul rispetto dei principali obblighi documentali e di organizzazione della sicurezza.</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Audit interni di sicurezza sul lavoro (SGSL).</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>BAA9911</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>ST24</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Avvenuto aggiornamento piattaforma "GOP" dei profili, qualifiche professionali del personale dipendente....</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Aggiornamento piattaforma "GOP" relativamente ai profili, qualifiche professionali del personale dipendente, anche in riferimento ai tempi di vestitizione e svestizione come da normativa vigente.</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>ST25</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Trasmissione flussi trimestrali pazienti preospedalizzati.</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Trasmissione flussi pazienti preospedalizzati anche in relazione ai pazienti in lista di attesa</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>BSU1405</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>Relazione UOSD referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>ST26</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Edizioni di corsi formazione attivati.</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Corso di informazione e formazione ai sensi e per gli effetti degli artt. 36, 37 del D.Lgs. 81/08 e s.m.i..</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>Flussi aziendali</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>ST27</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Percentuale di carte contabili residue  al 31/12/2025.</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Prosecuzione e conclusione delle azioni di regolarizzazione delle carte contabili propedeutiche alla certificabilità del bilancio (PAC).</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>BAA9902</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>Flussi aziendali</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>ST27B</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Percentuale di carte contabili residue  al 31/12/2025.</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Consultazione e supporto alle azioni di regolarizzazione delle carte contabili propedeutiche alla certificabilità del bilancio (PAC).</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>Relazione direzione referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>ST28</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Percentuale pratiche trattate.</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Comitato Valutazione dei Sinistri ai sensi del D.Lgs. 24 /2017 valutazione del contenzioso.</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>BAA9902</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>Software LegalPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>ST29</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Percentuale di somme pignorate recuperate del primo semestre anno 2022.</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Svincolo somme pignorate presso Tesoreria Aziendale.</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>BAA9902</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>Flussi aziendali</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>ST30</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Ispezioni periodiche del personale nella misura del 3%.</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Attività di controllo, con verifiche a campione, finalizzate all’accertamento dell’osservanza delle disposizioni normative sia in materia di incompatibilità che relativamente alla correttezza amministrativa nell’esercizio delle attività professionali.</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>BAA9003</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>ST31</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Ispezioni effettuate.</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Effettuazione di indagini ispettive su disposizione del D.G..</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>BAA9003</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>ST32</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Fatture pagate entro 15 gg.</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Rispetto dei tempi di pagamento. Monitoraggio tempi medi di ritardo aziendali.</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>BAA9905</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>Software S.A.P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>ST33</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Rilascio piattaforma e profilazione permissions accessi.</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Piattaforma condivisione report e dati interni.</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>ST34</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Percentuale di istanze relative al fabbisogno sanitario valutate.</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Valutare l'appropriatezza dei fabbisogni di beni di interesse sanitario (oltre alle tecnologie anche farmaci, dispositivi medici ed altri articoli sanitari).</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>BSU9095</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>ST35</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Percentuale di istanze valutate nei 10 gg..</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Tempestività nella valutare l'appropriatezza dei fabbisogni di beni di interesse sanitario (oltre alle tecnologie anche farmaci, dispositivi medici ed altri articoli sanitari).</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>BSU9095</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>ST36</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Percentuali bonifica liste di attesa ambulatoriali.</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Pulizia liste di attesa ambulatoriali.</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>BSA9090</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>CUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>ST37</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Numero di riunioni effettuate con il gruppo di supporto alla D.S..</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Promuovere le attività del gruppo di supporto alla Direzione Sanitaria per la valutazione delle tecnologie sanitarie.</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>BSU9095</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>Report UOS HTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>ST38</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Percentuale di bonifica liste di attesa ricovero chirurgico.</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Pulizia liste di attesa ricovero chirurgico.</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>BSA9090</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>CUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>ST39</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Invio informativa e report trimestrale alla Direzione Strategica.</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Monitoraggio dei tempi per il debito informativo nell'ambito dell'Azienda e vs tutti i canali di raccolta flussi dati.</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>Cruscotto Informativo Regionale per la Sanità (CIRS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>ST40</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Redazione regolamento attribuzione incarichi dirigenziali.</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Regolamento attribuzione incarichi dirigenziali.</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>Delibera di approvazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>ST41</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Predisposizione regolamento sui criteri generali relativi all’articolazione dell’orario di lavoro da sottoporre in sede di contrattazione integrativa aziendale.</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Regolamentazione orario di lavoro.</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>BAA9903</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>Delibera di approvazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>ST42</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Percentuale di flussi informativi per il monitoraggio del personale (DCA 53/2019) inviati nei tempi previsti.</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Rispetto dei tempi per il debito informativo nell'ambito dell'Azienda e vs tutti i canali di raccolta flussi dati.</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>BAA9908</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>UOC Pianificazione e Controllo di Gestione</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>ST43</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Redazione regolamento e procedure di scarto dei documenti d'archivio, amministrativi e sanitari.</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Regolamento e procedure di scarto dei documenti d'archivio, amministrativi e sanitari.</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>Delibera di approvazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>ST44</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Redazione manuale per la gestione del sistema documentario ai sensi del paragrafo 3.5 delle Linee Guida sulla Formazione e conservazione dei documenti informatici di AGID.</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Manuale per la gestione del sistema documentario informatico ai sensi del paragrafo 3.5 delle Linee Guida sulla Formazione e conservazione dei documenti informatici di AGID.</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>Delibera di approvazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>ST45</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Gestione contratti relativi ai rapporti di locazione attivi e passivi, con azioni conseguenti in caso di eventuale mancato pagamento.</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Monitoraggio contratti relativi ai rapporti di locazione attivi e passivi.</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>BAA9904</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>ST46</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Percentuale pratiche trattate.</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Comitato Valutazione dei Sinistri ai sensi del D.Lgs. 24 /2017 valutazione del contenzioso.</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>ST46B</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Percentuale pratiche trattate.</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Comitato Valutazione dei Sinistri ai sensi del D.Lgs. 24 /2017 valutazione del contenzioso.</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>BSU4500</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>ST47</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Produzione report quadrimestrale sull'attività di monitoraggio da inviare alla D.A..</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Monitoraggio sistematico sull'attività di pubblicazione nella sezione "Amministrazione trasparente (RPCT)" .</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>Report UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>ST48</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Predisposzione del regolamento per la gestione delle segnalazione trasmesse dagli utenti all'URP .</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Regolamento sulle segnalazioni ricevute dall'URP.</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>Pubblicazione delibera</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>ST49</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Attivazione e monitoraggio piano del percorso chirurgico.</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Applicazione e controllo del rispetto dei percorsi indicati dal piano di gestione del percorso del paziente chirurgico programmato.</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>BSU1405</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>Relazione UOSD referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>ST50</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Adozione procedura d'impatto sulla protezione dei dati.</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Procedura per Valutazione d'impatto sulla protezione dei dati.</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>Pubblicazione Procedura</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>ST51</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Percentuale di interventi di manutenzione su guasto blocante apparecchiature elettromedicali effettuati.</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Interventi di manutenzione su chiamata per guasto bloccante sulle apparecchiature elettromedicali.</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>BAA9910</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>Software EASI</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>ST52</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Percentuale di interventi di manutenzione preventiva apparecchiature elettromedicali effettuati.</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Interventi di manutenzione programmata sulle apparecchiature elettromedicali.</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>Software EASI</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>ST53</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Definizione e coordinamento capitolato di gara. Delibera di indizione</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Procedura di gara per l'acquisizione in Noleggio di Colonne endoscopiche ed Ecoendoscopiche per le UU.OO. Endoscopia e Pneumologia Interventistica</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>Delibera di approvazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>ST54</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Avvnuta istruttoria e predisposizione della documentazione relativa alle richieste di risarcimento danni.</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Istruttoria e predisposizione della documentazione relativa alle richieste di risarcimento danni.</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>BSA9090</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>Relazione Direzione Sanitaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>ST55</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Percentuale transazioni effettuate…</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Transazione  festivi infrasettimanali area comparto.</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>ST56</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Stesura e definizione degli atti interni.</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Definizione degli atti di indirizzo, circolari e disposizioni della direzione strategica.</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>Relazione Direzione referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>ST56B</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Stesura e definizione degli atti interni.</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Definizione degli atti di indirizzo, circolari e disposizioni della direzione strategica.</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>Relazione Direzione referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>ST57</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Avvenuta gestione flusso documentale...</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Gestione flusso documentale, protocollazione, archiviazione, tenuta registri, produzione di provvedimenti ed atti, attività di ricerca e studio, rapporti con interlocutori interni ed esterni.</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>Relazione Direzione referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>ST57B</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Avvenuta gestione flusso documentale...</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Gestione flusso documentale, protocollazione, archiviazione, tenuta registri, produzione di provvedimenti ed atti, attività di ricerca e studio, rapporti con interlocutori interni ed esterni e dematerializzazione dell'archivio amministrativo.</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>Relazione Direzione referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>ST58</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Invio raccomandate circolarizzabili recupero crediti anno 2025 e precedenti, evidenza semestrale somme rientrate.</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Monitoraggio del processo di recupero crediti codici bianchi.</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>Flussi aziendali e software S.A.P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>ST59</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Percentuale di carte contabili residue  al 31/12/2026.</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Prosecuzione e conclusione delle azioni di regolarizzazione delle carte contabili propedeutiche alla certificabilità del bilancio (PAC-DCA27/2019)</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>BAA9905</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>Software INBIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>ST60</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Monitoraggio e controllo del processo di certificabilità delle giacenze di magazzino con report trimestrale alla direzione strategica.</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Certificabilità delle giacenze di magazzino.</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>BAA9905</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>Certificazione direttori UUOO coinvolte</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>ST61</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Definizione e coordinamento capitolato di gara.</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Procedura di  gara per i servizi RIS (sistema di refertazione bio-immagini aziendale).</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>ST62</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Avvenuta gestione flusso presso altre aziende….</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Gestione del flusso verso altre Aziende, delle prestazioni sanitarie non previste da Convenzioni: dall’autorizzazione delle richieste all’emissione di NSO per la liquidazione del ciclo passivo delle fatture.</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>BSA9090</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>Relazione Direzione referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>ST63</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Interventi mirati a digitalizzare differenti tipologie di referti e documenti clinici in formato PDF/A con HL7 CDA2 iniettato e firmati digitalmente con firma PaDES.</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Incremento della tipologia di referti e documenti clinici digitalizzati per l'alimentazione del Fascicolo Sanitario Elettronico.</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>BAA9909</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>ST64</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Aggiornamento annuale della programmazione degli acquisti di beni e servizi secondo modalità e tempistiche definite dall'art.37 D.Lgs. 36/2023.</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Programmazione triennale degli acquisti di beni e servizi.</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>ST65</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Pubblicazione delibere di indizione/aggiudicazione delle gare già in proroga indette ed indizione di quelle ancora non indette.</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Completamento, con la contrattualizzazione, di tutte le gare in proroga già indette ed indizione di quelle ancora non indette.</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>ST66</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Stesura di linee guida e regolamenti aziendali in linea con gli adempimenti contrattuali previsti dall'AQ Sicurezza da remoto, di compliance e di controllo per le PA Lotto 2.</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Redazione di policy aziendali per la sicurezza informatica.</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>BAA9909</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>ST67</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Espletamento gara RIS.</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Indizione ed espletamento gara RIS.</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>BAA9906</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>Pubblicazione delibera</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>ST68</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Avvenuta installazione della nuova segnaletica entro il 30 giugno 2026.</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Predisposizione della nuova segnaletica interna al Padiglione Monumentale N</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>BAA9912</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>ST69</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Completamento del percorso formativo obbligatorio sul Fascicolo Sanitario Elettronico (FSE) previsto per il personale sanitario tenuto all’adempimento, con monitoraggio intermedio dello stato di avanzamento al 15/03 e rendicontazione finale al 15/06</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Piano di Formazione FSE 2.0 - intervento PNRR - Missione 6 "Salute", Componente 2 sub-investimento 1.31 (b) "Adozione e utilizzo del Fascicolo Sanitario Elettronico da parte delle Regioni - Change management"</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>BSU4700</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>ST69B</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Completamento del percorso formativo obbligatorio sul Fascicolo Sanitario Elettronico (FSE) previsto per il personale sanitario tenuto all’adempimento, con monitoraggio intermedio dello stato di avanzamento al 15/03 e rendicontazione finale al 15/06</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Piano di Formazione FSE 2.0 - intervento PNRR - Missione 6 "Salute", Componente 2 sub-investimento 1.31 (b) "Adozione e utilizzo del Fascicolo Sanitario Elettronico da parte delle Regioni - Change management"</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>BSU4700</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>ST70</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Aggiornamento annuale programmazione dei lavori secondo modalità e tempistiche definite dall'art.37 D.Lgs. 36/2023 - servizi e forniture.</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Programmazione triennale dei lavori - servizi e forniture.</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>BAA9907</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>ST70B</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Aggiornamento annuale programmazione dei lavori secondo modalità e tempistiche definite dall'art.37 D.Lgs. 36/2023.</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Programmazione triennale dei lavori.</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>ST71</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Presentazione pratiche presso il competente comando dei VVFF.</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Redazione aggiornamenti esami progetto VVFF ex DM 19/03/2015.</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>BAA9903</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>ST72</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Avvenuto avvio delle opere…</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Avvio cantieri programmati, quali Padiglione N "Accoglienza", la Banca del tessuto muscolo scheletrico presso il Padiglione H e l'impianto di depurazione dell'intera Azienda Ospedaliera.</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>ST73</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Numero di giorni di permanenza media di un dispositivo medico in magazzino.</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Giacenza media magazzino dispositivi medici.</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>BSTA4800-1</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>Flussi aziendali</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>ST73B</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Numero di giorni di permanenza media di un dispositivo medico in magazzino.</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Giacenza media magazzino dispositivi medici.</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>BSTA4800-1</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>Flussi aziendali</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>ST74</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Aggiornamento annuale della programmazione degli acquisti di beni e servizi secondo modalità e tempistiche definite dall'art.37 D.Lgs. 36/2023.</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Programmazione triennale degli acquisti di beni e servizi.</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>ST75</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Percentuale di flussi informativi inviati.</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Gestione flussi informativi piattaforma STRIMS.</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>BSTA1002</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>Flussi aziendali</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>ST76</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Somma di studi multicentrici/trial clinici attivi (con pazienti arruolati e/o follow-up) e
+studi/progetti di ricerca clinica finanziati in cui l'UOC svolge il ruolo di Principal Investigator (PI), anno 2026.</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Valorizzazione partecipazione a Trial e Studi in corso.
+Riconoscimento di Principal Investigator in progetti finanziati.</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>Direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>ST77</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Percentuale di lavoratori sottoposti a visite mediche e controlli programmati.</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Copertura della Sorveglianza Sanitaria</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>BAA9911</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>ST78</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Avvenuta attivazione percorso  trasmigrazione codici SDO da IC9 a IC10..</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Attivazione percorso,in qualità di referenti regionali, trasmigrazione codici SDO da IC9 a IC10.</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>BSA9090</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>ST79</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Ispezioni effettuate</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Effettuazione di indagini ispettive su disposizione della Direzione Strategica sulla presenza in servizio del personale</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>ST80</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Revisione di almeno quattro PDTA</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Revisione di Percorsi Diagnostici Terapeutici Assistenziali (PDTA)</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>BSU9095</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>Report UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>ST81</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Attivazione di percorso per presa in carico del paziente con malattia rara</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Presa in carico del paziente con malattia rara</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>BSU9095</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>ST82</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Tempo medio di evasione delle richieste di consulenza.</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Miglioramento dell'appropriatezza e tempestività delle consulenze nutrizionali per pazienti ricoverati.</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>BAA9909</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>Software Wirgilio</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>ST83</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Produzione bimestrale report a livello aziendale da condividere con la direzione strategica e i direttori di dipartimento in ottemperanza al piano aziendale di sovraffollamento.</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Gestione sovraffolamento Pronto Soccorso OBI.</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>BSU1409</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>Report UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>ST84</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Rendicontazione bimestrale.</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Monitoraggio della presa in carico del paziente dimissibile a strutture territoriali con elaborazione di indicatore di interesse strategico.</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>BSU1409</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>Report UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>ST85</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Avvenuta stipula dei contratti/accordi collettivi decentrati integrativi, assicurando la definizione degli istituti contrattuali e la piena conformità alle disposizioni normative e agli indirizzi dell’amministrazione.</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Stipula dei contratti/accordi collettivi decentrati integrativi, assicurando la definizione degli istituti contrattuali e la piena conformità alle disposizioni normative e agli indirizzi dell’amministrazione.</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>BAA9903</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>ST86</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Espletamento procedura di gara per l’implementazione di un sistema aziendale di tracciamento dei dispositivi medici…</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Procedura di appalto del sistema di tracciamento dei dispositivi medici</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>BAA9909</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>ST87</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Avvenuta rendicontazione PNRR relativa alle attività svolte nel 2025, assicurando la verifica delle operazioni e la coerenza con i requisiti di monitoraggio e controllo.</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Rendicontazione PNRR relativa alle attività svolte nel 2025, assicurando la verifica delle operazioni e la coerenza con i requisiti di monitoraggio e controllo.</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>BAA9909</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>ST87B</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Avvenuta rendicontazione PNRR relativa alle attività svolte nel 2026, assicurando la verifica delle operazioni e la coerenza con i requisiti di monitoraggio e controllo.</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Rendicontazione PNRR relativa alle attività svolte nel 2026, assicurando la verifica delle operazioni e la coerenza con i requisiti di monitoraggio e controllo.</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>ST87C</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Avvenuta rendicontazione PNRR relativa alle attività svolte nel 2026, assicurando la verifica delle operazioni e la coerenza con i requisiti di monitoraggio e controllo.</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Rendicontazione PNRR relativa alle attività svolte nel 2026, assicurando la verifica delle operazioni e la coerenza con i requisiti di monitoraggio e controllo.</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>ST88</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Avvenuta rendicontazione PNRR relativa alle attività svolte nel 2026, assicurando la verifica delle operazioni e la coerenza con i requisiti di monitoraggio e controllo.</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Garantire la chiusura della rendicontazione PNRR relativa alle attività svolte nel 2026 assicurando la verifica delle operazioni e la coerenza con i requisiti di monitoraggio e controllo.</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>ST89</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Percentuale di pazienti stranieri con dati anagrafici correttamente rilevati.</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Completezza ed accuratezza nel rilevamento dei dati di pazienti stranieri per il rimborso dei DRG</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>BSU7200</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>flussi aziendali</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>ST90</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Avvvenuta implementazione nuovo protocollo informatizzato entro la data del 31.03.</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Implementazione nuovo protocollo informatizzato entro la data del 31.03.</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>BAA9904</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>ST91</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Percentuale convenzioni stipulate nei tempi previsti e report trimestrale monitoraggio capienza economica (da inviare alla D.A. e D.S.).</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Stipula convenzioni nei tempi previsti con monitoraggio della capienza economica.</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>BAA9904</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>Software UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>ST92</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Definizione procedura di gara farmaci antiblastici con affidamento entro il 30/05</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Procedura di gara farmaci antiblastici</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>BAA9910</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>ST93</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Redazione regolamento attribuzione incarichi dirigenziali area TPA.</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Regolamento attribuzione incarichi dirigenziali area TPA.</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>BAA9903</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>ST94</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Report quadrimestrale da inviare alla D.A.</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Monitoraggio costante scadenze contrattuali ed indizione relative procedure.</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>BAA9906</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>ST95</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Report trimestrale dei consumi</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Monitoraggio consumi energetici.</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>BAA9913</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>ST96</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Realizzazione dello Studio di Fattibilità Tecnica Economica</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Attività propedeutiche alla realizzazione della centrale del freddo</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>SI_NO</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>BAA9913</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>Relazione UOC referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>ST97</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Numero di report bimestrali trasmessi entro la scadenza prevista (30/06/2026) sull’avanzamento dei percorsi formativi FSE 2.0.</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Monitoraggio dell’avanzamento dei percorsi formativi FSE 2.0.</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>ST98</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Numero di report trimestrali trasmessi alle UU.OO aziendali.</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Monitoraggio dei consumi di farmaci e dispositivi per UU.OO.</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>Relazione direzione UOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>ST99</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Interventi mirati a digitalizzare i referti di televisita con firma digitale</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Incremento del numero di referti di visita specialistica erogata in modalità remota prodotti in formato digitale</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>AREA_SERV_STR</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>BAA9909</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>Piattaforma TM Sinfonia</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>XXX</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Partecipazione del 50% dei dirigenti medici al corso sulla comunicazione e percorso fine vita.</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Attività formativa sulla comunicazione e percorso fine vita.</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>BSU4700</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>Flussi aziendali</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>XXXX</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Partecipazione del 50% dei dirigenti medici al corso sulla comunicazione e percorso fine vita.</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Attività formativa sulla comunicazione e percorso fine vita.</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>AREA_APPR</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>BSU4700</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>Flussi aziendali</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="E1:E236"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/script/templates/IndicatoriCatalogo_BS.xlsx
+++ b/script/templates/IndicatoriCatalogo_BS.xlsx
@@ -1504,7 +1504,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>A/B*100</t>
+          <t>(A-B)/B*100</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SI_NO</t>
+          <t>(A-B)/B*100</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>A/B*100</t>
+          <t>A/B</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5394,6 +5394,11 @@
           <t>Promuovere le attività del gruppo di supporto alla Direzione Sanitaria per la valutazione delle tecnologie sanitarie.</t>
         </is>
       </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>A/B*100</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>AREA_SERV_STR</t>
@@ -5783,7 +5788,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>SI_NO</t>
+          <t>A/B*100</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -6079,7 +6084,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>A/B*100</t>
+          <t>SI_NO</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -6294,11 +6299,6 @@
           <t>Piano di Formazione FSE 2.0 - intervento PNRR - Missione 6 "Salute", Componente 2 sub-investimento 1.31 (b) "Adozione e utilizzo del Fascicolo Sanitario Elettronico da parte delle Regioni - Change management"</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>SI_NO</t>
-        </is>
-      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>AREA_SERV_STR</t>
@@ -7563,11 +7563,6 @@
           <t>Giacenze fisiche del magazzino farmaceutico e le giacenze fisiche presso tutti i reparti dell'azienda.</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>A/B*100</t>
-        </is>
-      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>AREA_SERV_SAN</t>
@@ -8541,7 +8536,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>A/B*100</t>
+          <t>A/B</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -8578,7 +8573,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>A/B*100</t>
+          <t>A/B</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -8615,7 +8610,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>A/B*100</t>
+          <t>A/B</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -11334,7 +11329,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>A/B*100</t>
+          <t>A/B</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -13327,7 +13322,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>A/B*100</t>
+          <t>SI_NO</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -13682,7 +13677,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>A/B*100</t>
+          <t>A/B</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -13719,7 +13714,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>A/B*100</t>
+          <t>A/B</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -13822,7 +13817,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>A/B*100</t>
+          <t>SUM(A)</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -14029,7 +14024,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>A/B*100</t>
+          <t>A/B</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
